--- a/Result/profitability/1443.xlsx
+++ b/Result/profitability/1443.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.28</v>
       </c>
       <c r="M2" t="n">
-        <v>0.25625</v>
+        <v>0.26</v>
       </c>
       <c r="N2" t="n">
-        <v>41.15125</v>
+        <v>40.80125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>0.215</v>
+        <v>0.24</v>
       </c>
       <c r="N3" t="n">
-        <v>35.93375</v>
+        <v>36.58875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0.185</v>
+        <v>0.1725</v>
       </c>
       <c r="N4" t="n">
-        <v>30.775</v>
+        <v>30.745</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07749999999999999</v>
+        <v>0.19375</v>
       </c>
       <c r="N5" t="n">
-        <v>24.24</v>
+        <v>23.74375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>0.12375</v>
+        <v>0.1225</v>
       </c>
       <c r="N6" t="n">
-        <v>17.6175</v>
+        <v>17.43375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.12</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05124999999999998</v>
+        <v>0.03125</v>
       </c>
       <c r="N7" t="n">
-        <v>11.90375</v>
+        <v>11.79125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.06</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0325</v>
+        <v>-0.04125</v>
       </c>
       <c r="N8" t="n">
-        <v>6.565</v>
+        <v>6.465</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1443</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>238</v>
+      </c>
+      <c r="D75" t="n">
+        <v>126</v>
+      </c>
+      <c r="E75" t="n">
+        <v>112</v>
+      </c>
+      <c r="F75" t="n">
+        <v>46.89</v>
+      </c>
+      <c r="G75" t="n">
+        <v>84</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>35.21%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>86</v>
+      </c>
+      <c r="K75" t="n">
+        <v>61</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="N75" t="n">
+        <v>47.5075</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1346153846153846</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.7999999999999972</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.01677500524218911</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.9299999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.9375</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.969999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.07805741250491538</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
